--- a/education_surveys/029_early_childhood_credential_pathways_survey--education_surveys.xlsx
+++ b/education_surveys/029_early_childhood_credential_pathways_survey--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1138,7 +1138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -1455,17 +1455,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>form_early_childhood_credential_choices</t>
+          <t>form_early_childhood_credential_status_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>child_and_youth_care_(cyc)</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Child and Youth Care (CYC)</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1477,12 +1477,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1494,29 +1494,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>expired</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Expired</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>form_early_childhood_credential_status_choices</t>
+          <t>form_early_childhood_credential_type_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>child_development_associate_(cda)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Expired</t>
+          <t>Child Development Associate (CDA)</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>child_development_associate_(cda)</t>
+          <t>child_and_youth_care_(cyc)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Child Development Associate (CDA)</t>
+          <t>Child and Youth Care (CYC)</t>
         </is>
       </c>
     </row>
@@ -1545,29 +1545,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>child_and_youth_care_(cyc)</t>
+          <t>early_childhood_education_and_care_(ecec)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Child and Youth Care (CYC)</t>
+          <t>Early Childhood Education and Care (ECEC)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>form_early_childhood_credential_type_choices</t>
+          <t>form_survey_completed_by_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>early_childhood_education_and_care_(ecec)</t>
+          <t>user</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Early Childhood Education and Care (ECEC)</t>
+          <t>User</t>
         </is>
       </c>
     </row>
@@ -1579,29 +1579,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>auto-generated</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>Auto-generated</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>form_survey_completed_by_choices</t>
+          <t>form_survey_status_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>auto-generated</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Auto-generated</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Incomplete</t>
         </is>
       </c>
     </row>
@@ -1630,29 +1630,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Incomplete</t>
+          <t>Submitted</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>form_survey_status_choices</t>
+          <t>form_survey_type_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>form</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Form</t>
         </is>
       </c>
     </row>
@@ -1664,29 +1664,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>form</t>
+          <t>survey</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Form</t>
+          <t>Survey</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>form_survey_type_choices</t>
+          <t>form_survey_completed_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>survey</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Survey</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1698,29 +1698,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>form_survey_completed_choices</t>
+          <t>form_survey_incomplete_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1732,29 +1732,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>form_survey_incomplete_choices</t>
+          <t>form_survey_submitted_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1766,29 +1766,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>form_survey_submitted_choices</t>
+          <t>form_survey_status_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1800,12 +1800,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Incomplete</t>
         </is>
       </c>
     </row>
@@ -1817,29 +1817,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Incomplete</t>
+          <t>Submitted</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>form_survey_status_choices</t>
+          <t>form_survey_completed_by_utc_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>user</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>User</t>
         </is>
       </c>
     </row>
@@ -1851,27 +1851,10 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>auto-generated</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>form_survey_completed_by_utc_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>auto-generated</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
         <is>
           <t>Auto-generated</t>
         </is>
